--- a/naver-place-crawler/results_health/해운대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>빔스짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>vimsgym_3@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1310-1516</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 선수촌로 95 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://www.instagram.com/vims_gym_3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>425</v>
+        <v>596</v>
       </c>
       <c r="Q2" t="n">
-        <v>977</v>
+        <v>67</v>
       </c>
       <c r="R2" t="n">
-        <v>1402</v>
+        <v>663</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,24 +636,24 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1097711832</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1097711832</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="Q3" t="n">
-        <v>1387</v>
+        <v>1420</v>
       </c>
       <c r="R3" t="n">
-        <v>2846</v>
+        <v>2886</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,39 +752,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더플래닛짐 헬스&amp;PT 해운대 장산역점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>theplanetgym@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1310-5564</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로 77 성부빌딩 8층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>191</v>
+        <v>430</v>
       </c>
       <c r="Q4" t="n">
-        <v>273</v>
+        <v>957</v>
       </c>
       <c r="R4" t="n">
-        <v>464</v>
+        <v>1387</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1992573620</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스 &amp; PT 마린시티점</t>
+          <t>헬짐 헬스&amp;PT 센텀시티점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>hellgym_centum@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1380-2436</t>
+          <t>0507-1494-3739</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://blog.naver.com/hellgym_centum</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>461</v>
       </c>
       <c r="Q5" t="n">
-        <v>202</v>
+        <v>1238</v>
       </c>
       <c r="R5" t="n">
-        <v>272</v>
+        <v>1699</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +918,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2055602485</t>
+          <t>1986332432</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055602485</t>
+          <t>https://m.place.naver.com/place/1986332432</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>정석피트니스 재송점 헬스 PT</t>
+          <t>라이트짐 장산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>standard_jaesong@naver.com</t>
+          <t>busan91@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1358-4896</t>
+          <t>0507-1438-1740</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 재반로 116 8층 정석피트니스</t>
+          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/standardfitness_jaesong</t>
+          <t>https://open.kakao.com/o/sOS9sPTf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>338</v>
+        <v>734</v>
       </c>
       <c r="Q6" t="n">
-        <v>213</v>
+        <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>551</v>
+        <v>1178</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1888176177</t>
+          <t>1418968603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1888176177</t>
+          <t>https://m.place.naver.com/place/1418968603</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>정석피트니스 해운대점 헬스 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>standardfitness@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-5843</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 구남로 21 301동 5층 505호</t>
+          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standardfitness/223890826938</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>106</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="n">
-        <v>131</v>
+        <v>474</v>
       </c>
       <c r="R7" t="n">
-        <v>237</v>
+        <v>778</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1106,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1560924378</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1560924378</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬짐 헬스&amp;PT 센텀시티점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hellgym_centum@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1494-3739</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 335 6층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgym_centum</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="Q8" t="n">
-        <v>1235</v>
+        <v>156</v>
       </c>
       <c r="R8" t="n">
-        <v>1695</v>
+        <v>632</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1986332432</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986332432</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에프원 피트니스 헬스&amp;PT 반여점</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>f1_banyeo@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-8723</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 명장로67번길 131 2층</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f1_banyeo</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,18 +1259,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>204</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>495</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1231839879</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231839879</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>정석피트니스 반여점 헬스 PT</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>standard_banyeo@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1380-4896</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 선수촌로 58 2층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/standardfitness__banyeo</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1357,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>166</v>
+        <v>270</v>
       </c>
       <c r="R10" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,1051 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1085556615</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1085556615</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>올바른운동 해운대좌동점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yesmyt@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1391-3259</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 좌동순환로 181 5층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://abrtraining.kr/</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>278</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>612</v>
-      </c>
-      <c r="R11" t="n">
-        <v>890</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1715982137</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1715982137</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>그래비티짐 해운대 장산점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>acmilan0@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1397-0149</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/acmilan0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>475</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>149</v>
-      </c>
-      <c r="R12" t="n">
-        <v>624</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1743697484</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>핏 라이프스타일 해운대</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>tmzjwl27@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>isj89858@gmail.com</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 세실로69번길 15 7F 핏 라이프스타일</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/1FE2ojnmHyYiv3OlukWegw9jtzBYKObAA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>403</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1057</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1460</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1236047384</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1236047384</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>모션업PT 체형관리센터</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>motionuppt2879@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1362-1057</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 좌동순환로 506 영풍리젠시 403호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2067</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2141</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1186141561</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1186141561</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>베스트피트니스 해운대 중동점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>vastt_seomyeon@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1321-1145</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 좌동순환로 473 로데오아울렛 B동 4층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/vastt_seomyeon</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>903</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1178</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2081</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1587891622</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1587891622</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>F45 센텀시티</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>f45centumcity@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1475-0463</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 센텀3로 26 센텀스퀘어빌딩 5층 501호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/f45_centumcity</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>265</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>128</v>
-      </c>
-      <c r="R16" t="n">
-        <v>393</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1305428352</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1305428352</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>라이트짐 장산점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>busan91@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1438-1740</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://open.kakao.com/o/sOS9sPTf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>728</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>446</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1174</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1418968603</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1418968603</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>저스트플레이짐</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>just_haeundae@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1356-5638</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 해운대로 814 6층 601호</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/just_haeundae</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>550</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>520</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1070</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1282442899</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1282442899</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>스탠다드짐 재송점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>standardgym3@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1469-3544</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 해운대로91번길 21-5 지하층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/standard___gym3/?igsh=aXlodWoyMjEwMQ%3D%3D&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>355</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>108</v>
-      </c>
-      <c r="R19" t="n">
-        <v>463</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2033075748</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2033075748</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>쑥피트니스 좌동점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ssookfit_jwadong@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1430-1723</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 좌동순환로 175 2층 201호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ssookfit_jwadong</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>278</v>
-      </c>
-      <c r="R20" t="n">
-        <v>446</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2018463791</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2018463791</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>젬스톤피트니스 해운대 장산점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>magic6740@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1373-5091</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 좌동로 96 B동 4층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/gemstone_haeundae</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>669</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1025</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1694</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1701680165</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1701680165</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대구_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="39" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빔스짐</t>
+          <t>우노짐 헬스&amp;PT 마린시티점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vimsgym_3@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1310-1516</t>
+          <t>0507-1419-1786</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 선수촌로 95 지하1층</t>
+          <t>부산 해운대구 마린시티2로 33 104동 B107-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vims_gym_3</t>
+          <t>https://www.instagram.com/uno_gym_3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpkopem</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>596</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>663</v>
+        <v>26</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1097711832</t>
+          <t>2066839617</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097711832</t>
+          <t>https://m.place.naver.com/place/2066839617</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>빔스짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>vimsgym_3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1310-1516</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 선수촌로 95 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://www.instagram.com/vims_gym_3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1466</v>
+        <v>597</v>
       </c>
       <c r="Q3" t="n">
-        <v>1420</v>
+        <v>68</v>
       </c>
       <c r="R3" t="n">
-        <v>2886</v>
+        <v>665</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1097711832</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1097711832</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>430</v>
+        <v>1469</v>
       </c>
       <c r="Q4" t="n">
-        <v>957</v>
+        <v>1422</v>
       </c>
       <c r="R4" t="n">
-        <v>1387</v>
+        <v>2891</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -928,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>라이트짐 장산점</t>
+          <t>뉴피트니스 2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>busan91@naver.com</t>
+          <t>rational12074@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1438-1740</t>
+          <t>0507-1478-3602</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산광역시 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOS9sPTf</t>
+          <t>https://www.instagram.com/new____fitness_2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +992,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>734</v>
+        <v>175</v>
       </c>
       <c r="Q6" t="n">
-        <v>444</v>
+        <v>237</v>
       </c>
       <c r="R6" t="n">
-        <v>1178</v>
+        <v>412</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1016,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1418968603</t>
+          <t>1020154888</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418968603</t>
+          <t>https://m.place.naver.com/place/1020154888</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>쑥피트니스 해운대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ssookfitness_hd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1308-8420</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ssookfitness_hd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,10 +1080,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f0d6</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>398</v>
       </c>
       <c r="Q7" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="R7" t="n">
-        <v>778</v>
+        <v>882</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1114,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1246026577</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1246026577</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>라이트짐 장산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>busan91@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1438-1740</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://open.kakao.com/o/sOS9sPTf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1173,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1184,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>476</v>
+        <v>736</v>
       </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>444</v>
       </c>
       <c r="R8" t="n">
-        <v>632</v>
+        <v>1180</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1418968603</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1418968603</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1269,12 +1277,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>475</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>779</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1320,93 +1328,285 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/acmilan0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>477</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>157</v>
+      </c>
+      <c r="R10" t="n">
+        <v>634</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1743697484</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1743697484</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>언로드 PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unloadpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1320-4232</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2024136684</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024136684</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>태리짐 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ansth1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1419-2400</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q12" t="n">
         <v>270</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>320</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1346702700</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
